--- a/exports/KALYANKJIL_full_report.xlsx
+++ b/exports/KALYANKJIL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>8.06</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>67.84999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="I2" t="n">
         <v>66.12587661449305</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.77</v>
+        <v>-8.49</v>
       </c>
       <c r="L2" t="n">
-        <v>5.68</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>0.64</v>
       </c>
       <c r="N2" t="n">
-        <v>1.68</v>
+        <v>3.61</v>
       </c>
       <c r="O2" t="n">
         <v>-0.07000000000000001</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>7.35</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>66.84999999999999</v>
+        <v>69.75</v>
       </c>
       <c r="I3" t="n">
         <v>68.55878945272214</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.53</v>
+        <v>-6.98</v>
       </c>
       <c r="L3" t="n">
-        <v>3.99</v>
+        <v>8.44</v>
       </c>
       <c r="M3" t="n">
         <v>0.98</v>
       </c>
       <c r="N3" t="n">
-        <v>1.75</v>
+        <v>4.41</v>
       </c>
       <c r="O3" t="n">
         <v>-3.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,22 +695,22 @@
         <v>7.41</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44599.55208333334</v>
+        <v>44600.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>65.90000000000001</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>65.73579440798729</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.52</v>
+        <v>-6.59</v>
       </c>
       <c r="L4" t="n">
-        <v>6.31</v>
+        <v>7.46</v>
       </c>
       <c r="M4" t="n">
         <v>-0</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>7.02</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44623.55208333334</v>
+        <v>44624.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>59.9</v>
+        <v>62.55</v>
       </c>
       <c r="I5" t="n">
         <v>60.04334705221407</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>8.06</v>
+        <v>3.99</v>
       </c>
       <c r="L5" t="n">
         <v>1.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44673.55208333334</v>
+        <v>44676.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>63.2</v>
+        <v>62</v>
       </c>
       <c r="I6" t="n">
         <v>62.10564637466906</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>52</v>
       </c>
       <c r="K6" t="n">
-        <v>1.04</v>
+        <v>-0.88</v>
       </c>
       <c r="L6" t="n">
         <v>7.43</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>6.54</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44692.38541666666</v>
+        <v>44692.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>55.9</v>
+        <v>66</v>
       </c>
       <c r="I7" t="n">
         <v>62.10000778383336</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>9.84</v>
+        <v>-6.45</v>
       </c>
       <c r="L7" t="n">
-        <v>2.82</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>1.45</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>18.46</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44728.55208333334</v>
+        <v>44729.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>57.9</v>
+        <v>57.4</v>
       </c>
       <c r="I8" t="n">
         <v>57.4086138789526</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K8" t="n">
-        <v>-12.27</v>
+        <v>-13.03</v>
       </c>
       <c r="L8" t="n">
         <v>15.68</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>5.43</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>58.9</v>
+        <v>60.3</v>
       </c>
       <c r="I9" t="n">
         <v>59.22456631641219</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.61</v>
+        <v>-5.05</v>
       </c>
       <c r="L9" t="n">
-        <v>3.66</v>
+        <v>6.27</v>
       </c>
       <c r="M9" t="n">
         <v>1.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.02</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44882.38541666666</v>
+        <v>44882.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>100.9</v>
+        <v>100.5</v>
       </c>
       <c r="I10" t="n">
         <v>100.8142313581491</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>142</v>
+        <v>142.1666666666667</v>
       </c>
       <c r="K10" t="n">
-        <v>67.33</v>
+        <v>66.67</v>
       </c>
       <c r="L10" t="n">
         <v>3.81</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>192</v>
+        <v>193</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>6</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>5.93</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44888.38541666666</v>
+        <v>44888.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>96.3</v>
+        <v>99.8</v>
       </c>
       <c r="I11" t="n">
         <v>97.85809916448832</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>5.833333333333333</v>
+        <v>6</v>
       </c>
       <c r="K11" t="n">
-        <v>4.18</v>
+        <v>0.7</v>
       </c>
       <c r="L11" t="n">
         <v>1.19</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S11" t="b">
+        <v>0</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>10</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44917.55208333334</v>
+        <v>44918.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>122.2</v>
+        <v>110.8</v>
       </c>
       <c r="I12" t="n">
         <v>119.3138598948157</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>22.44</v>
+        <v>11.02</v>
       </c>
       <c r="L12" t="n">
         <v>3.51</v>
@@ -1125,7 +1268,7 @@
         <v>0.25</v>
       </c>
       <c r="N12" t="n">
-        <v>5.16</v>
+        <v>10.88</v>
       </c>
       <c r="O12" t="n">
         <v>8.77</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>18.8</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44922.55208333334</v>
+        <v>44923.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>123.7</v>
+        <v>128.25</v>
       </c>
       <c r="I13" t="n">
         <v>125.1080796336393</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>-11.64</v>
+        <v>-15.75</v>
       </c>
       <c r="L13" t="n">
-        <v>13.45</v>
+        <v>17.33</v>
       </c>
       <c r="M13" t="n">
         <v>0.93</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>14.52</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44951.55208333334</v>
+        <v>44953.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>116.4</v>
+        <v>110.3</v>
       </c>
       <c r="I14" t="n">
         <v>113.2983228585252</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K14" t="n">
-        <v>-9.24</v>
+        <v>-14</v>
       </c>
       <c r="L14" t="n">
-        <v>10.96</v>
+        <v>17.66</v>
       </c>
       <c r="M14" t="n">
         <v>0.59</v>
       </c>
       <c r="N14" t="n">
-        <v>4.91</v>
+        <v>5.11</v>
       </c>
       <c r="O14" t="n">
         <v>7.11</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>10.55</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>113.8</v>
+        <v>118.1</v>
       </c>
       <c r="I15" t="n">
         <v>117.0829127809868</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.17</v>
+        <v>-7.07</v>
       </c>
       <c r="L15" t="n">
         <v>8.16</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.74</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44970.55208333334</v>
+        <v>44971.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>108.5</v>
+        <v>105</v>
       </c>
       <c r="I16" t="n">
         <v>106.6428716917453</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-8.130000000000001</v>
+        <v>-11.09</v>
       </c>
       <c r="L16" t="n">
-        <v>11.01</v>
+        <v>12.36</v>
       </c>
       <c r="M16" t="n">
         <v>0.75</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>12.16</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44974.55208333334</v>
+        <v>44977.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>110.75</v>
+        <v>116.85</v>
       </c>
       <c r="I17" t="n">
         <v>116.5430354294424</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.48</v>
+        <v>-11.29</v>
       </c>
       <c r="L17" t="n">
-        <v>7.57</v>
+        <v>11.81</v>
       </c>
       <c r="M17" t="n">
         <v>1.09</v>
       </c>
       <c r="N17" t="n">
-        <v>4.4</v>
+        <v>7.45</v>
       </c>
       <c r="O17" t="n">
         <v>-2.49</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>11.22</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>116.75</v>
+        <v>108.1</v>
       </c>
       <c r="I18" t="n">
         <v>112.4649637995004</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09</v>
+        <v>-7.49</v>
       </c>
       <c r="L18" t="n">
-        <v>5.18</v>
+        <v>7.96</v>
       </c>
       <c r="M18" t="n">
         <v>1.14</v>
       </c>
       <c r="N18" t="n">
-        <v>2.5</v>
+        <v>6.81</v>
       </c>
       <c r="O18" t="n">
         <v>7.45</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>12.42</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>114.9</v>
+        <v>122</v>
       </c>
       <c r="I19" t="n">
         <v>116.938613776033</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.29</v>
+        <v>-12.86</v>
       </c>
       <c r="L19" t="n">
-        <v>7.96</v>
+        <v>13.32</v>
       </c>
       <c r="M19" t="n">
         <v>1.25</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>11.74</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45012.55208333334</v>
+        <v>45013.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>117.6</v>
+        <v>108.2</v>
       </c>
       <c r="I20" t="n">
         <v>109.8123653818571</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.61</v>
+        <v>-11.31</v>
       </c>
       <c r="L20" t="n">
-        <v>7.17</v>
+        <v>13.36</v>
       </c>
       <c r="M20" t="n">
-        <v>0.86</v>
+        <v>4.76</v>
       </c>
       <c r="N20" t="n">
-        <v>2.83</v>
+        <v>8.25</v>
       </c>
       <c r="O20" t="n">
         <v>11.93</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.51</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45048.38541666666</v>
+        <v>45048.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>103.25</v>
+        <v>105.8</v>
       </c>
       <c r="I21" t="n">
         <v>105.5366178314223</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>4.57</v>
+        <v>2.22</v>
       </c>
       <c r="L21" t="n">
         <v>3.51</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>6.07</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="I22" t="n">
         <v>227.2630799021454</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>133</v>
+        <v>133.8333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>118.34</v>
+        <v>111.72</v>
       </c>
       <c r="L22" t="n">
         <v>2.65</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>12.86</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45203.55208333334</v>
+        <v>45204.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>226.6</v>
+        <v>231.9</v>
       </c>
       <c r="I23" t="n">
         <v>229.1580371670307</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.16</v>
+        <v>-3.53</v>
       </c>
       <c r="L23" t="n">
         <v>7.17</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45246.38541666666</v>
+        <v>45246.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>315.1</v>
+        <v>312.95</v>
       </c>
       <c r="I24" t="n">
         <v>314.3098466353204</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K24" t="n">
-        <v>35.88</v>
+        <v>34.95</v>
       </c>
       <c r="L24" t="n">
         <v>1.72</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>12.05</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45279.55208333334</v>
+        <v>45280.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>315.7</v>
+        <v>335.8</v>
       </c>
       <c r="I25" t="n">
         <v>334.30299208323</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>33</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.88</v>
+        <v>-7.3</v>
       </c>
       <c r="L25" t="n">
         <v>8.960000000000001</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45310.55208333334</v>
+        <v>45311.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>364.9</v>
+        <v>361.8</v>
       </c>
       <c r="I26" t="n">
         <v>361.9997664042412</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K26" t="n">
-        <v>8.67</v>
+        <v>7.74</v>
       </c>
       <c r="L26" t="n">
         <v>6.42</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>8.01</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45334.38541666666</v>
+        <v>45334.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>359.7</v>
+        <v>365.05</v>
       </c>
       <c r="I27" t="n">
         <v>363.4423936817611</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>23</v>
+        <v>23.16666666666667</v>
       </c>
       <c r="K27" t="n">
-        <v>0.58</v>
+        <v>-0.9</v>
       </c>
       <c r="L27" t="n">
         <v>4.81</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>12.12</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="I28" t="n">
         <v>373.8560433316221</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>29</v>
+        <v>29.83333333333333</v>
       </c>
       <c r="K28" t="n">
-        <v>5.19</v>
+        <v>-0.01</v>
       </c>
       <c r="L28" t="n">
-        <v>3.29</v>
+        <v>3.53</v>
       </c>
       <c r="M28" t="n">
         <v>0.82</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>13.95</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45377.55208333334</v>
+        <v>45378.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="I29" t="n">
         <v>407.1604334236393</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K29" t="n">
-        <v>-9.039999999999999</v>
+        <v>-12.05</v>
       </c>
       <c r="L29" t="n">
         <v>12.32</v>
@@ -2094,7 +2441,7 @@
         <v>1.78</v>
       </c>
       <c r="N29" t="n">
-        <v>3.38</v>
+        <v>4.76</v>
       </c>
       <c r="O29" t="n">
         <v>-1.35</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>11.35</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45404.38541666666</v>
+        <v>45404.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>406.4</v>
+        <v>403</v>
       </c>
       <c r="I30" t="n">
         <v>403.8903239327044</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.64</v>
+        <v>-1.47</v>
       </c>
       <c r="L30" t="n">
         <v>3.77</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>8.25</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>406.15</v>
+        <v>410.35</v>
       </c>
       <c r="I31" t="n">
         <v>407.9805852705107</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>46</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.78</v>
+        <v>-1.82</v>
       </c>
       <c r="L31" t="n">
         <v>5.46</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>10.01</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>559.8</v>
+        <v>525.3</v>
       </c>
       <c r="I32" t="n">
         <v>525.3644179397658</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K32" t="n">
-        <v>36.42</v>
+        <v>28.01</v>
       </c>
       <c r="L32" t="n">
         <v>3.01</v>
       </c>
       <c r="M32" t="n">
-        <v>0.33</v>
+        <v>4.43</v>
       </c>
       <c r="N32" t="n">
-        <v>2.56</v>
+        <v>4.07</v>
       </c>
       <c r="O32" t="n">
         <v>0.48</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>13.18</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45525.55208333334</v>
+        <v>45526.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>556</v>
+        <v>585.05</v>
       </c>
       <c r="I33" t="n">
         <v>584.606466729545</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K33" t="n">
-        <v>-5.84</v>
+        <v>-11.37</v>
       </c>
       <c r="L33" t="n">
-        <v>11.17</v>
+        <v>12.32</v>
       </c>
       <c r="M33" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="N33" t="n">
-        <v>3.15</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="O33" t="n">
         <v>-4.07</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>10.52</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45561.55208333334</v>
+        <v>45562.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>720</v>
+        <v>707.5</v>
       </c>
       <c r="I34" t="n">
         <v>707.9892585136633</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>36</v>
       </c>
       <c r="K34" t="n">
-        <v>23.07</v>
+        <v>20.93</v>
       </c>
       <c r="L34" t="n">
         <v>2.29</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.02</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45602.38541666666</v>
+        <v>45602.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>689.95</v>
+        <v>705</v>
       </c>
       <c r="I35" t="n">
         <v>701.4833396623571</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>2.48</v>
+        <v>0.35</v>
       </c>
       <c r="L35" t="n">
         <v>9.26</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.66</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45646.55208333334</v>
+        <v>45649.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>719.9</v>
+        <v>715.1</v>
       </c>
       <c r="I36" t="n">
         <v>716.6133276505286</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>44</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K36" t="n">
-        <v>2.11</v>
+        <v>1.43</v>
       </c>
       <c r="L36" t="n">
         <v>8.84</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>8.9</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45657.55208333334</v>
+        <v>45658.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>761.3</v>
+        <v>772.25</v>
       </c>
       <c r="I37" t="n">
         <v>765.0601202543069</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-6.46</v>
+        <v>-7.99</v>
       </c>
       <c r="L37" t="n">
         <v>8.24</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>8.23</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45664.38541666666</v>
+        <v>45664.55208333334</v>
       </c>
       <c r="H38" t="n">
-        <v>736.7</v>
+        <v>719.3</v>
       </c>
       <c r="I38" t="n">
         <v>727.0903433610985</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.6</v>
+        <v>-6.86</v>
       </c>
       <c r="L38" t="n">
-        <v>6.44</v>
+        <v>7.01</v>
       </c>
       <c r="M38" t="n">
         <v>0.17</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>11.83</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>503</v>
+        <v>514.05</v>
       </c>
       <c r="I39" t="n">
         <v>507.1496494101012</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K39" t="n">
-        <v>30.07</v>
+        <v>28.53</v>
       </c>
       <c r="L39" t="n">
         <v>2.93</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,22 +3179,22 @@
         <v>15.95</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45702.38541666666</v>
+        <v>45702.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>491.6</v>
+        <v>484.45</v>
       </c>
       <c r="I40" t="n">
         <v>486.433052907684</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K40" t="n">
-        <v>-4.37</v>
+        <v>-5.76</v>
       </c>
       <c r="L40" t="n">
-        <v>5.85</v>
+        <v>6.59</v>
       </c>
       <c r="M40" t="n">
         <v>0.99</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>15.36</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45736.38541666666</v>
+        <v>45736.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>455.35</v>
+        <v>464</v>
       </c>
       <c r="I41" t="n">
         <v>457.7390703180544</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>33.83333333333334</v>
+        <v>34</v>
       </c>
       <c r="K41" t="n">
-        <v>6.01</v>
+        <v>4.22</v>
       </c>
       <c r="L41" t="n">
         <v>5.26</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.03</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45818.55208333334</v>
+        <v>45819.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>547.8</v>
+        <v>539.45</v>
       </c>
       <c r="I42" t="n">
         <v>542.8820403716506</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>82</v>
+        <v>82.83333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>18.06</v>
+        <v>16.26</v>
       </c>
       <c r="L42" t="n">
         <v>4.52</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>4</v>
+      </c>
+      <c r="U42" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.6</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45832.55208333334</v>
+        <v>45833.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>521.5</v>
+        <v>538.6</v>
       </c>
       <c r="I43" t="n">
         <v>538.4586039039983</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K43" t="n">
-        <v>3.33</v>
+        <v>0.16</v>
       </c>
       <c r="L43" t="n">
         <v>1.9</v>
@@ -2892,7 +3407,7 @@
         <v>0.48</v>
       </c>
       <c r="N43" t="n">
-        <v>1.64</v>
+        <v>3.51</v>
       </c>
       <c r="O43" t="n">
         <v>-2.23</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>7.1</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45876.55208333334</v>
+        <v>45877.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>598.1</v>
+        <v>540.6</v>
       </c>
       <c r="I44" t="n">
         <v>575.0955760426979</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K44" t="n">
-        <v>11.05</v>
+        <v>0.37</v>
       </c>
       <c r="L44" t="n">
         <v>3.19</v>
@@ -2949,7 +3476,7 @@
         <v>2.54</v>
       </c>
       <c r="N44" t="n">
-        <v>2.18</v>
+        <v>11.08</v>
       </c>
       <c r="O44" t="n">
         <v>3.51</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>17.76</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45916.55208333334</v>
+        <v>45917.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>506</v>
+        <v>528.05</v>
       </c>
       <c r="I45" t="n">
         <v>523.4100587578436</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K45" t="n">
-        <v>6.4</v>
+        <v>2.32</v>
       </c>
       <c r="L45" t="n">
         <v>13.95</v>
@@ -3006,7 +3545,7 @@
         <v>2.83</v>
       </c>
       <c r="N45" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="O45" t="n">
         <v>-11.08</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>6.33</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45922.55208333334</v>
+        <v>45923.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>505.8</v>
+        <v>497.95</v>
       </c>
       <c r="I46" t="n">
         <v>500.1417671655321</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.21</v>
+        <v>-5.7</v>
       </c>
       <c r="L46" t="n">
-        <v>4.55</v>
+        <v>5.88</v>
       </c>
       <c r="M46" t="n">
         <v>0.22</v>
       </c>
       <c r="N46" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="O46" t="n">
         <v>3.56</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>5.65</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45933.38541666666</v>
+        <v>45933.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>480.7</v>
+        <v>490.55</v>
       </c>
       <c r="I47" t="n">
         <v>483.3815951798074</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>3.46</v>
+        <v>1.49</v>
       </c>
       <c r="L47" t="n">
         <v>1.8</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.18</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45974.38541666666</v>
+        <v>45974.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>501.4</v>
+        <v>499</v>
       </c>
       <c r="I48" t="n">
         <v>500.684898357489</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>40.83333333333334</v>
+        <v>41</v>
       </c>
       <c r="K48" t="n">
-        <v>2.21</v>
+        <v>1.72</v>
       </c>
       <c r="L48" t="n">
         <v>4.79</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>5.82</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>494.6</v>
+        <v>506.75</v>
       </c>
       <c r="I49" t="n">
         <v>505.8894945956582</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>0.88</v>
+        <v>-1.55</v>
       </c>
       <c r="L49" t="n">
         <v>3.07</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>6.39</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>492.15</v>
+        <v>478.35</v>
       </c>
       <c r="I50" t="n">
         <v>485.16152770733</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.88</v>
+        <v>-5.6</v>
       </c>
       <c r="L50" t="n">
-        <v>4.13</v>
+        <v>5.79</v>
       </c>
       <c r="M50" t="n">
         <v>0.19</v>
       </c>
       <c r="N50" t="n">
-        <v>1.88</v>
+        <v>3.61</v>
       </c>
       <c r="O50" t="n">
         <v>2.24</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46015.55208333334</v>
+        <v>46017.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>487.75</v>
+        <v>494.6</v>
       </c>
       <c r="I51" t="n">
         <v>490.4107738463882</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K51" t="n">
-        <v>-1.97</v>
+        <v>-3.4</v>
       </c>
       <c r="L51" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="M51" t="n">
         <v>0.78</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>5.38</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>493</v>
+        <v>485.6</v>
       </c>
       <c r="I52" t="n">
         <v>489.4211876566953</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.32</v>
+        <v>-1.82</v>
       </c>
       <c r="L52" t="n">
-        <v>3.05</v>
+        <v>3.86</v>
       </c>
       <c r="M52" t="n">
         <v>0.55</v>
       </c>
       <c r="N52" t="n">
-        <v>1.84</v>
+        <v>2.45</v>
       </c>
       <c r="O52" t="n">
         <v>0.5600000000000001</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,28 +4076,28 @@
         <v>6.76</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>380.5</v>
+        <v>428.15</v>
       </c>
       <c r="I53" t="n">
         <v>399.6179641353777</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K53" t="n">
-        <v>21.64</v>
+        <v>11.83</v>
       </c>
       <c r="L53" t="n">
         <v>1.6</v>
       </c>
       <c r="M53" t="n">
-        <v>5.45</v>
+        <v>6.44</v>
       </c>
       <c r="N53" t="n">
-        <v>4.36</v>
+        <v>14.59</v>
       </c>
       <c r="O53" t="n">
         <v>-2.45</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>14.99</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>396.35</v>
+        <v>385.05</v>
       </c>
       <c r="I54" t="n">
         <v>391.4774067705609</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-7.43</v>
+        <v>-10.07</v>
       </c>
       <c r="L54" t="n">
-        <v>9.52</v>
+        <v>10.77</v>
       </c>
       <c r="M54" t="n">
         <v>3.61</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>7.81</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46105.55208333334</v>
+        <v>46106.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>372.15</v>
+        <v>395.8</v>
       </c>
       <c r="I55" t="n">
         <v>391.4131131543991</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K55" t="n">
-        <v>3.35</v>
+        <v>-2.79</v>
       </c>
       <c r="L55" t="n">
         <v>5.13</v>
@@ -3576,7 +4235,7 @@
         <v>3.18</v>
       </c>
       <c r="N55" t="n">
-        <v>2.39</v>
+        <v>5.28</v>
       </c>
       <c r="O55" t="n">
         <v>-1.45</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>10.6</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46133.38541666666</v>
+        <v>46133.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>417</v>
+        <v>414.9</v>
       </c>
       <c r="I56" t="n">
         <v>415.4592531361037</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>5.36</v>
+        <v>4.83</v>
       </c>
       <c r="L56" t="n">
         <v>5.66</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>7.47</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46177.55208333334</v>
+        <v>46178.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>363.65</v>
+        <v>371</v>
       </c>
       <c r="I57" t="n">
         <v>368.9300645980646</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>44</v>
+        <v>44.83333333333334</v>
       </c>
       <c r="K57" t="n">
-        <v>12.35</v>
+        <v>10.58</v>
       </c>
       <c r="L57" t="n">
         <v>3.35</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,22 +4421,22 @@
         <v>8.41</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46182.55208333334</v>
+        <v>46183.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>355.3</v>
+        <v>345.25</v>
       </c>
       <c r="I58" t="n">
         <v>345.328681013446</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>-4.23</v>
+        <v>-6.94</v>
       </c>
       <c r="L58" t="n">
-        <v>5.39</v>
+        <v>7.35</v>
       </c>
       <c r="M58" t="n">
         <v>2.19</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>9.56</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>345.2</v>
+        <v>381.45</v>
       </c>
       <c r="I59" t="n">
         <v>360.1015386726619</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>0.01</v>
+        <v>-10.49</v>
       </c>
       <c r="L59" t="n">
-        <v>3.14</v>
+        <v>10.85</v>
       </c>
       <c r="M59" t="n">
         <v>2.04</v>
       </c>
       <c r="N59" t="n">
-        <v>4.21</v>
+        <v>10.81</v>
       </c>
       <c r="O59" t="n">
         <v>-4.83</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>13.28</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46209.55208333334</v>
+        <v>46210.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>381.25</v>
+        <v>357.35</v>
       </c>
       <c r="I60" t="n">
         <v>368.0194403945527</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.05</v>
+        <v>-6.32</v>
       </c>
       <c r="L60" t="n">
-        <v>8</v>
+        <v>8.68</v>
       </c>
       <c r="M60" t="n">
-        <v>0.57</v>
+        <v>5.35</v>
       </c>
       <c r="N60" t="n">
-        <v>2.1</v>
+        <v>6.49</v>
       </c>
       <c r="O60" t="n">
         <v>10.81</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.35</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46211.55208333334</v>
+        <v>46212.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>375</v>
+        <v>438.6</v>
       </c>
       <c r="I61" t="n">
         <v>383.2460173914205</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.94</v>
+        <v>-22.74</v>
       </c>
       <c r="L61" t="n">
-        <v>8.130000000000001</v>
+        <v>23.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0.98</v>
+        <v>1.33</v>
       </c>
       <c r="N61" t="n">
-        <v>5.19</v>
+        <v>17.27</v>
       </c>
       <c r="O61" t="n">
         <v>-6.49</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>18.26</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46238.55208333334</v>
+        <v>46239.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>591.4</v>
+        <v>567.05</v>
       </c>
       <c r="I62" t="n">
         <v>587.8037765766268</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K62" t="n">
-        <v>34.84</v>
+        <v>29.29</v>
       </c>
       <c r="L62" t="n">
         <v>13.85</v>
@@ -3975,7 +4718,7 @@
         <v>2.02</v>
       </c>
       <c r="N62" t="n">
-        <v>2.91</v>
+        <v>3.75</v>
       </c>
       <c r="O62" t="n">
         <v>17.27</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>11.65</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46240.55208333334</v>
+        <v>46241.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>598</v>
+        <v>622</v>
       </c>
       <c r="I63" t="n">
         <v>621.265661390846</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K63" t="n">
-        <v>-5.46</v>
+        <v>-9.69</v>
       </c>
       <c r="L63" t="n">
-        <v>5.81</v>
+        <v>11.1</v>
       </c>
       <c r="M63" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="N63" t="n">
         <v>5.05</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>10.66</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46265.55208333334</v>
+        <v>46266.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>614.8</v>
+        <v>576.4</v>
       </c>
       <c r="I64" t="n">
         <v>593.0217021663177</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K64" t="n">
-        <v>-1.16</v>
+        <v>-7.33</v>
       </c>
       <c r="L64" t="n">
-        <v>5.94</v>
+        <v>7.91</v>
       </c>
       <c r="M64" t="n">
-        <v>0.08</v>
+        <v>0.87</v>
       </c>
       <c r="N64" t="n">
-        <v>2.41</v>
+        <v>6.8</v>
       </c>
       <c r="O64" t="n">
         <v>1.05</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>10.64</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46272.55208333334</v>
+        <v>46273.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>590.5</v>
+        <v>612.6</v>
       </c>
       <c r="I65" t="n">
         <v>607.8517657636269</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K65" t="n">
-        <v>-2.45</v>
+        <v>-6.28</v>
       </c>
       <c r="L65" t="n">
-        <v>6.63</v>
+        <v>7.04</v>
       </c>
       <c r="M65" t="n">
         <v>0.65</v>
       </c>
       <c r="N65" t="n">
-        <v>2.81</v>
+        <v>4.18</v>
       </c>
       <c r="O65" t="n">
         <v>-6.8</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>8.970000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>579.15</v>
+        <v>572.5</v>
       </c>
       <c r="I66" t="n">
         <v>578.0747606545175</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-5.46</v>
+        <v>-6.55</v>
       </c>
       <c r="L66" t="n">
-        <v>6.24</v>
+        <v>6.9</v>
       </c>
       <c r="M66" t="n">
         <v>0.92</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.48</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46301.55208333334</v>
+        <v>46302.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>549.35</v>
+        <v>569.8</v>
       </c>
       <c r="I67" t="n">
         <v>562.7743446724927</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>4.04</v>
+        <v>0.47</v>
       </c>
       <c r="L67" t="n">
         <v>1.64</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,22 +5111,22 @@
         <v>10.51</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46317.38541666666</v>
+        <v>46317.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>534</v>
+        <v>531.15</v>
       </c>
       <c r="I68" t="n">
         <v>532.6053738898893</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>15</v>
+        <v>15.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>-6.28</v>
+        <v>-6.78</v>
       </c>
       <c r="L68" t="n">
-        <v>6.7</v>
+        <v>6.98</v>
       </c>
       <c r="M68" t="n">
         <v>0.35</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>7</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26.1</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>142</v>
+        <v>142.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.4</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44</v>
+        <v>45.6</v>
       </c>
     </row>
     <row r="11">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>5.33</v>
+        <v>1.35</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9.02</v>
+        <v>5.61</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.53</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>118.34</v>
+        <v>111.72</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47.8</v>
+        <v>37.3</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.9</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5.39</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15.68</v>
+        <v>23.6</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="25">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.56</v>
+        <v>5.87</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>13.73</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
